--- a/Documentos Base/Sprint 6 documentacion/Sprint_06_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 6 documentacion/Sprint_06_Backlog_ICARO.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 6 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B3522E-776C-4C22-92A7-55733436C363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6184C09-E5B4-43B2-B24A-87535454E4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
     <sheet name="RESUMEN DE VELOCIDAD " sheetId="5" r:id="rId2"/>
-    <sheet name="GLOSARIO" sheetId="6" r:id="rId3"/>
+    <sheet name="Resumen de casos de prueba " sheetId="7" r:id="rId3"/>
+    <sheet name="GLOSARIO" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="267">
   <si>
     <t>ID</t>
   </si>
@@ -448,13 +449,388 @@
   </si>
   <si>
     <t>SPRINT BACKLOG — Sprint 06</t>
+  </si>
+  <si>
+    <t>ID CP</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Evidencia</t>
+  </si>
+  <si>
+    <t>Grupo 1</t>
+  </si>
+  <si>
+    <t>Bandeja Gerencial</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Grupo 2</t>
+  </si>
+  <si>
+    <t>Aprobación/Rechazo</t>
+  </si>
+  <si>
+    <t>Grupo 3</t>
+  </si>
+  <si>
+    <t>Grupo 4</t>
+  </si>
+  <si>
+    <t>Grupo 5</t>
+  </si>
+  <si>
+    <t>CP-087</t>
+  </si>
+  <si>
+    <t>Catálogo de Materiales</t>
+  </si>
+  <si>
+    <t>GET /materiales sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 01</t>
+  </si>
+  <si>
+    <t>CP-088</t>
+  </si>
+  <si>
+    <t>GET /materiales con Residente → 200/401 OK, solo activos por defecto</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 02</t>
+  </si>
+  <si>
+    <t>CP-089</t>
+  </si>
+  <si>
+    <t>GET /materiales?soloActivos=false con Admin → incluye inactivos</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 03</t>
+  </si>
+  <si>
+    <t>CP-090</t>
+  </si>
+  <si>
+    <t>POST /materiales sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 04</t>
+  </si>
+  <si>
+    <t>CP-091</t>
+  </si>
+  <si>
+    <t>POST /materiales con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 05</t>
+  </si>
+  <si>
+    <t>CP-092</t>
+  </si>
+  <si>
+    <t>POST /materiales con Admin y campos incompletos → valida campos obligatorios</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 06</t>
+  </si>
+  <si>
+    <t>CP-093</t>
+  </si>
+  <si>
+    <t>PUT /materiales/:id para desactivar con Bodeguero → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 07</t>
+  </si>
+  <si>
+    <t>CP-094</t>
+  </si>
+  <si>
+    <t>PUT /materiales/:id con Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 08</t>
+  </si>
+  <si>
+    <t>CP-095</t>
+  </si>
+  <si>
+    <t>DELETE /materiales/:id con Admin → soft-delete permitido</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 09</t>
+  </si>
+  <si>
+    <t>CP-096</t>
+  </si>
+  <si>
+    <t>Gestión de Proyectos</t>
+  </si>
+  <si>
+    <t>PATCH /proyectos/:id/estado sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 10</t>
+  </si>
+  <si>
+    <t>CP-097</t>
+  </si>
+  <si>
+    <t>PATCH /proyectos/:id/estado con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 11</t>
+  </si>
+  <si>
+    <t>CP-098</t>
+  </si>
+  <si>
+    <t>PATCH /proyectos/:id/estado con estado inválido → 400/401</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 12</t>
+  </si>
+  <si>
+    <t>CP-099</t>
+  </si>
+  <si>
+    <t>PATCH /proyectos/:id/estado INACTIVO con Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 13</t>
+  </si>
+  <si>
+    <t>CP-100</t>
+  </si>
+  <si>
+    <t>PUT /proyectos/:id con Admin → edición completa permitida</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 14</t>
+  </si>
+  <si>
+    <t>CP-101</t>
+  </si>
+  <si>
+    <t>Requerimientos de Compra</t>
+  </si>
+  <si>
+    <t>POST /compras/proyectos/:id/requerimientos sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 15</t>
+  </si>
+  <si>
+    <t>CP-102</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con Contador → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 16</t>
+  </si>
+  <si>
+    <t>CP-103</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con Bodeguero → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 17</t>
+  </si>
+  <si>
+    <t>CP-104</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con justificación vacía → 400 Bad Request</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 18</t>
+  </si>
+  <si>
+    <t>CP-105</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con detalles vacíos → 400 Bad Request</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 19</t>
+  </si>
+  <si>
+    <t>CP-106</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con cantidad decimal → 400, debe ser entero positivo</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 20</t>
+  </si>
+  <si>
+    <t>CP-107</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con cantidad cero → 400 Bad Request</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 21</t>
+  </si>
+  <si>
+    <t>CP-108</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con cantidad negativa → 400 Bad Request</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 22</t>
+  </si>
+  <si>
+    <t>CP-109</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con Admin + body completo → pasa RBAC</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 23</t>
+  </si>
+  <si>
+    <t>CP-110</t>
+  </si>
+  <si>
+    <t>CA: si se crea un requerimiento exitoso, el estado inicial es EN_REVISION</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 24</t>
+  </si>
+  <si>
+    <t>CP-111</t>
+  </si>
+  <si>
+    <t>Notificaciones</t>
+  </si>
+  <si>
+    <t>NotificationService emite evento requerimiento:creado al crear requerimiento válido</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 25</t>
+  </si>
+  <si>
+    <t>CP-112</t>
+  </si>
+  <si>
+    <t>emitirRequerimientoCreado no lanza excepciones, comportamiento fire-and-forget</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 26</t>
+  </si>
+  <si>
+    <t>CP-113</t>
+  </si>
+  <si>
+    <t>GET /compras/bandeja-gerencial sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 27</t>
+  </si>
+  <si>
+    <t>CP-114</t>
+  </si>
+  <si>
+    <t>GET /compras/bandeja-gerencial con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 28</t>
+  </si>
+  <si>
+    <t>CP-115</t>
+  </si>
+  <si>
+    <t>GET /compras/bandeja-gerencial con Contador → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 29</t>
+  </si>
+  <si>
+    <t>CP-116</t>
+  </si>
+  <si>
+    <t>GET /compras/bandeja-gerencial con Presidente/Gerente → pasa auth</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 30</t>
+  </si>
+  <si>
+    <t>CP-117</t>
+  </si>
+  <si>
+    <t>GET /compras/bandeja-gerencial con Admin → pasa auth</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 31</t>
+  </si>
+  <si>
+    <t>CP-118</t>
+  </si>
+  <si>
+    <t>PUT /compras/requerimientos/:id/aprobar sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 32</t>
+  </si>
+  <si>
+    <t>CP-119</t>
+  </si>
+  <si>
+    <t>PUT .../aprobar con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 33</t>
+  </si>
+  <si>
+    <t>CP-120</t>
+  </si>
+  <si>
+    <t>PUT .../aprobar con Presidente/Gerente → pasa RBAC</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 34</t>
+  </si>
+  <si>
+    <t>CP-121</t>
+  </si>
+  <si>
+    <t>PUT .../rechazar con Admin sin comentario → 400/401, comentario obligatorio</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 35</t>
+  </si>
+  <si>
+    <t>CP-122</t>
+  </si>
+  <si>
+    <t>PUT .../rechazar con Bodeguero → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>sprint6_requerimientos.test.js – Test 36</t>
+  </si>
+  <si>
+    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 06 (CP-087 a CP-122)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -560,8 +936,30 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -594,8 +992,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -683,11 +1093,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -752,6 +1259,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -811,10 +1361,11 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="40% - Énfasis3" xfId="1" builtinId="39"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -968,6 +1519,172 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -991,6 +1708,21 @@
     <tableColumn id="4" xr3:uid="{BADFBE41-FF57-4AD3-BC4F-F242468847E1}" name="Observación" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AED80A8-BF34-4B24-AEC4-BBFEB19738BB}" name="Tabla1" displayName="Tabla1" ref="A2:F38" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+  <autoFilter ref="A2:F38" xr:uid="{4AED80A8-BF34-4B24-AEC4-BBFEB19738BB}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{54079A7F-CD92-45AA-AB82-3F29A19FD291}" name="ID CP" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{7DC279D3-98F0-48EC-B1FF-228A3DE379E2}" name="Grupo" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{AC265AB3-3482-44FC-B11D-0F1EDDE2939C}" name="Módulo" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{FEA9C31D-1E1C-4955-9CCE-3060E1732EEB}" name="Descripción" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{31D47F46-E48C-4AD0-8BBE-D25F321761D9}" name="Estado" dataDxfId="6" dataCellStyle="40% - Énfasis3"/>
+    <tableColumn id="6" xr3:uid="{DF0482AA-8615-4139-A19A-B5DF140E34E3}" name="Evidencia" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1295,124 +2027,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="42"/>
       <c r="G3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="30"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="52">
         <v>46160</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="27"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="42"/>
       <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="37">
+      <c r="H4" s="52">
         <v>46164</v>
       </c>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="42"/>
     </row>
     <row r="5" spans="1:12" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="39"/>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="27"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="42"/>
     </row>
     <row r="6" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="42"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -1643,13 +2375,13 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
       <c r="F13" s="6">
         <v>42</v>
       </c>
@@ -1692,12 +2424,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
     </row>
     <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1925,6 +2657,777 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F91085-8AE0-45E8-8D0B-A89A8B6D3E01}">
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="78.42578125" customWidth="1"/>
+    <col min="6" max="6" width="39.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA982D7-F45A-4F02-8026-4725A48667D9}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1935,11 +3438,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
